--- a/results/Int All Data 0.1/Linea_fi_explain.xlsx
+++ b/results/Int All Data 0.1/Linea_fi_explain.xlsx
@@ -1694,10 +1694,10 @@
         <v>0.02218116213081561</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01469839957403616</v>
+        <v>0.01470612456437992</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007810362385631263</v>
+        <v>0.007806533901710895</v>
       </c>
       <c r="J3" t="n">
         <v>0.001904532851435391</v>
@@ -1715,7 +1715,7 @@
         <v>0.002692750701417545</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004966221773727817</v>
+        <v>0.004962429585635287</v>
       </c>
       <c r="P3" t="n">
         <v>0.002856881402618696</v>
@@ -1781,7 +1781,7 @@
         <v>0.02042718611960587</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.02913952294880056</v>
+        <v>0.0291357177737625</v>
       </c>
       <c r="AL3" t="n">
         <v>0.008141099847673255</v>
@@ -1817,7 +1817,7 @@
         <v>0.0003650177952983102</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.001641457047851027</v>
+        <v>0.001645108015357416</v>
       </c>
       <c r="AX3" t="n">
         <v>0.00134746698318857</v>
@@ -1883,7 +1883,7 @@
         <v>0.00615575270864115</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.002778404259641263</v>
+        <v>0.002782485892294324</v>
       </c>
       <c r="BT3" t="n">
         <v>-0.0006406064626786446</v>
@@ -1892,16 +1892,16 @@
         <v>0.01248333833067971</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0003659405629290235</v>
+        <v>-0.0003589463279516902</v>
       </c>
       <c r="BW3" t="n">
         <v>0.0002800487781308292</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.002133649636858018</v>
+        <v>0.002130140864928193</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.003412146779574968</v>
+        <v>0.003415813812944971</v>
       </c>
       <c r="BZ3" t="n">
         <v>0.003412146779574968</v>
@@ -1910,10 +1910,10 @@
         <v>0.00381984827574412</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.008775263769051795</v>
+        <v>0.00877528707793411</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.001984861311546423</v>
+        <v>-0.001988942944199484</v>
       </c>
       <c r="CD3" t="n">
         <v>0.00112971166766748</v>
@@ -1922,7 +1922,7 @@
         <v>0.0008027164731808378</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0007527461979350146</v>
+        <v>0.0007375792078239006</v>
       </c>
       <c r="CG3" t="n">
         <v>0.4241435974759201</v>
@@ -1949,7 +1949,7 @@
         <v>0.002716827534227852</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.04866992838251129</v>
+        <v>0.0486737364556263</v>
       </c>
       <c r="CP3" t="n">
         <v>-0.0001564558925301596</v>
@@ -1988,7 +1988,7 @@
         <v>0.0003926951991595917</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0.0008356545287849925</v>
+        <v>-0.0008394626018999963</v>
       </c>
       <c r="DC3" t="n">
         <v>0.2914270939189164</v>
@@ -2054,7 +2054,7 @@
         <v>0.00222924256843078</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.001028415812930661</v>
+        <v>-0.001032278308102542</v>
       </c>
       <c r="DY3" t="n">
         <v>0.003370379677454675</v>
@@ -2093,7 +2093,7 @@
         <v>0.002945624256560155</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.01120429688522051</v>
+        <v>0.01120810061287361</v>
       </c>
       <c r="EL3" t="n">
         <v>-1.212495794421286e-05</v>
@@ -2102,7 +2102,7 @@
         <v>0.0005250362689125608</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.0005212440808200324</v>
+        <v>0.0005250362689125608</v>
       </c>
       <c r="EO3" t="n">
         <v>0.0002182026149569538</v>
@@ -2163,10 +2163,10 @@
         <v>0.04051713672127616</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01948314395239218</v>
+        <v>0.01948932597653494</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007514713589969509</v>
+        <v>0.00752234814775125</v>
       </c>
       <c r="J4" t="n">
         <v>0.008379995172680949</v>
@@ -2184,7 +2184,7 @@
         <v>0.008188191106490347</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003839517209614743</v>
+        <v>0.003836994835569501</v>
       </c>
       <c r="P4" t="n">
         <v>0.008585982615858936</v>
@@ -2250,7 +2250,7 @@
         <v>0.02754994942026039</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.02157693138488076</v>
+        <v>0.02157909533668236</v>
       </c>
       <c r="AL4" t="n">
         <v>0.01834481120595033</v>
@@ -2286,7 +2286,7 @@
         <v>0.008403472865076766</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.009481659913675484</v>
+        <v>0.009484400729651258</v>
       </c>
       <c r="AX4" t="n">
         <v>0.005471440632301498</v>
@@ -2352,7 +2352,7 @@
         <v>0.02405262808935598</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.01337899898694851</v>
+        <v>0.01337846462833649</v>
       </c>
       <c r="BT4" t="n">
         <v>0.002606288202085694</v>
@@ -2361,16 +2361,16 @@
         <v>0.02511032689144164</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003420110763886967</v>
+        <v>0.003411161043997629</v>
       </c>
       <c r="BW4" t="n">
         <v>0.0005444186898235287</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01041647669016133</v>
+        <v>0.0104170447730457</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.002581504904186608</v>
+        <v>0.002588810402711363</v>
       </c>
       <c r="BZ4" t="n">
         <v>0.002581504904186608</v>
@@ -2379,10 +2379,10 @@
         <v>0.009853129741034569</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.02442373489440686</v>
+        <v>0.02442849301664085</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.008169353780774201</v>
+        <v>0.008180399767274117</v>
       </c>
       <c r="CD4" t="n">
         <v>0.007699580916566337</v>
@@ -2391,7 +2391,7 @@
         <v>0.00242040140972323</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.004367577873058748</v>
+        <v>0.004383916749382221</v>
       </c>
       <c r="CG4" t="n">
         <v>0.1071857156479886</v>
@@ -2418,7 +2418,7 @@
         <v>0.01329304720343076</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.04733643456351923</v>
+        <v>0.04733181998135201</v>
       </c>
       <c r="CP4" t="n">
         <v>0.001638221325712509</v>
@@ -2457,7 +2457,7 @@
         <v>0.00150405777357229</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.01416080450590962</v>
+        <v>0.01415992271963684</v>
       </c>
       <c r="DC4" t="n">
         <v>0.140592205637893</v>
@@ -2523,7 +2523,7 @@
         <v>0.006030250995776214</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.003817752611030277</v>
+        <v>0.003814660940905705</v>
       </c>
       <c r="DY4" t="n">
         <v>0.02919927452153434</v>
@@ -2562,7 +2562,7 @@
         <v>0.01514124918419809</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.02900301064507331</v>
+        <v>0.029001651999592</v>
       </c>
       <c r="EL4" t="n">
         <v>0.0003426235687649854</v>
@@ -2571,7 +2571,7 @@
         <v>0.0008698902185380344</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0008620103148797215</v>
+        <v>0.0008698902185380344</v>
       </c>
       <c r="EO4" t="n">
         <v>0.001373245471756439</v>
@@ -2635,7 +2635,7 @@
         <v>-0.006024096385542133</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.005666156202143946</v>
+        <v>-0.005704441041347619</v>
       </c>
       <c r="J5" t="n">
         <v>-0.01114285714285709</v>
@@ -2830,7 +2830,7 @@
         <v>-0.004683929931454667</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.009436834094368329</v>
+        <v>-0.00939878234398781</v>
       </c>
       <c r="BW5" t="n">
         <v>-0.0004211332312404004</v>
@@ -2851,7 +2851,7 @@
         <v>-0.04122108456579443</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.0218775510204081</v>
+        <v>-0.02191836734693871</v>
       </c>
       <c r="CD5" t="n">
         <v>-0.01130136986301369</v>
@@ -2860,7 +2860,7 @@
         <v>-0.002739726027397249</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.005233219567690528</v>
+        <v>-0.005271141448615813</v>
       </c>
       <c r="CG5" t="n">
         <v>0.2883899233296824</v>
@@ -3188,7 +3188,7 @@
         <v>0.002545555459657168</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.01560710566370268</v>
+        <v>0.01559759272610755</v>
       </c>
       <c r="AL6" t="n">
         <v>-0.001535833458282021</v>
@@ -3290,7 +3290,7 @@
         <v>-0.001776329222750589</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0008435634933053576</v>
+        <v>0.0008537675749380109</v>
       </c>
       <c r="BT6" t="n">
         <v>-0.001951105152356245</v>
@@ -3299,7 +3299,7 @@
         <v>0.001063005967160924</v>
       </c>
       <c r="BV6" t="n">
-        <v>2.871362940275457e-05</v>
+        <v>1.914241960183638e-05</v>
       </c>
       <c r="BW6" t="n">
         <v>-2.853881278538084e-05</v>
@@ -3329,7 +3329,7 @@
         <v>-0.0004656149017970041</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0007215329037133789</v>
+        <v>-0.0007408453795727826</v>
       </c>
       <c r="CG6" t="n">
         <v>0.3312201993368147</v>
@@ -3774,7 +3774,7 @@
         <v>7.584376185061359e-05</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.0006220681873136402</v>
+        <v>0.0006045243276645185</v>
       </c>
       <c r="BY7" t="n">
         <v>0.002629480888833346</v>
@@ -3798,7 +3798,7 @@
         <v>0.0003616488496914316</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0005710351683189841</v>
+        <v>0.0005534913086698623</v>
       </c>
       <c r="CG7" t="n">
         <v>0.4163884406718584</v>
@@ -3969,7 +3969,7 @@
         <v>0.000631468200418811</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.001862909989138767</v>
+        <v>0.001881928627404267</v>
       </c>
       <c r="EL7" t="n">
         <v>8.771929824563096e-05</v>
@@ -4060,7 +4060,7 @@
         <v>0.00610600520995924</v>
       </c>
       <c r="O8" t="n">
-        <v>0.008036022464041743</v>
+        <v>0.008026541993810418</v>
       </c>
       <c r="P8" t="n">
         <v>0.002276856524873869</v>
@@ -4162,7 +4162,7 @@
         <v>0.004485769357967867</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.006101346288979825</v>
+        <v>0.006128728545277742</v>
       </c>
       <c r="AX8" t="n">
         <v>0.004049487838240764</v>
@@ -4267,7 +4267,7 @@
         <v>0.001434762983896448</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0009842703265617065</v>
+        <v>0.0009747501437741973</v>
       </c>
       <c r="CG8" t="n">
         <v>0.5142430359297036</v>
@@ -4333,7 +4333,7 @@
         <v>0.001543648858860969</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.00387090125169579</v>
+        <v>0.003861381068908282</v>
       </c>
       <c r="DC8" t="n">
         <v>0.3362521214565374</v>
@@ -4715,7 +4715,7 @@
         <v>0.02731939860652733</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.008030803080308058</v>
+        <v>0.008067473414008087</v>
       </c>
       <c r="BZ9" t="n">
         <v>0.008030803080308058</v>
@@ -4736,7 +4736,7 @@
         <v>0.006029579067121771</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.01092775944261094</v>
+        <v>0.01096442977631098</v>
       </c>
       <c r="CG9" t="n">
         <v>0.5904287901990812</v>
@@ -4916,7 +4916,7 @@
         <v>0.002161547212741777</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.002123625331816492</v>
+        <v>0.002161547212741777</v>
       </c>
       <c r="EO9" t="n">
         <v>0.002919984831247657</v>
